--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas 05.05.2025 a 11.05.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - Relatório de Recusas 05.05.2025 a 11.05.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92030ED-75D4-4F74-8BFE-7DC64F1A6ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F85ACCA-2C1F-4F46-AB05-B3B2991C42A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,79 +51,76 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>132276510</t>
+    <t>132365888</t>
   </si>
   <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Recusas Santander  06/05/2025</t>
-  </si>
-  <si>
-    <t>132275216</t>
-  </si>
-  <si>
-    <t>132275957</t>
-  </si>
-  <si>
-    <t>132332058</t>
-  </si>
-  <si>
-    <t>132367798</t>
-  </si>
-  <si>
-    <t>132337490</t>
-  </si>
-  <si>
-    <t>132387957</t>
-  </si>
-  <si>
-    <t>132250482</t>
-  </si>
-  <si>
-    <t>132251075</t>
-  </si>
-  <si>
-    <t>132254008</t>
-  </si>
-  <si>
-    <t>132256376</t>
-  </si>
-  <si>
-    <t>132260854</t>
-  </si>
-  <si>
-    <t>132256105</t>
-  </si>
-  <si>
-    <t>132333103</t>
-  </si>
-  <si>
-    <t>132297806</t>
-  </si>
-  <si>
-    <t>132333730</t>
-  </si>
-  <si>
-    <t>132331409</t>
-  </si>
-  <si>
-    <t>132389908</t>
-  </si>
-  <si>
-    <t>132273420</t>
-  </si>
-  <si>
-    <t>132275725</t>
-  </si>
-  <si>
-    <t>132279663</t>
-  </si>
-  <si>
-    <t>132280918</t>
-  </si>
-  <si>
-    <t>132279668</t>
+    <t>Recusas Santander  07/05/2025</t>
+  </si>
+  <si>
+    <t>132293583</t>
+  </si>
+  <si>
+    <t>132434735</t>
+  </si>
+  <si>
+    <t>132359501</t>
+  </si>
+  <si>
+    <t>132364489</t>
+  </si>
+  <si>
+    <t>132384015</t>
+  </si>
+  <si>
+    <t>132365063</t>
+  </si>
+  <si>
+    <t>132362812</t>
+  </si>
+  <si>
+    <t>132365156</t>
+  </si>
+  <si>
+    <t>132386295</t>
+  </si>
+  <si>
+    <t>132364624</t>
+  </si>
+  <si>
+    <t>132363520</t>
+  </si>
+  <si>
+    <t>132357992</t>
+  </si>
+  <si>
+    <t>132365085</t>
+  </si>
+  <si>
+    <t>132382561</t>
+  </si>
+  <si>
+    <t>132298362</t>
+  </si>
+  <si>
+    <t>132424157</t>
+  </si>
+  <si>
+    <t>132364304</t>
+  </si>
+  <si>
+    <t>132281203</t>
+  </si>
+  <si>
+    <t>132361295</t>
+  </si>
+  <si>
+    <t>132358100</t>
+  </si>
+  <si>
+    <t>132362352</t>
   </si>
   <si>
     <t>Relatório de Recusas 05.05.2025 a 11.05.2025</t>
@@ -574,7 +571,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -592,7 +589,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -610,7 +607,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -628,7 +625,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -645,8 +642,8 @@
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>32</v>
+      <c r="D6" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -664,7 +661,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -681,8 +678,8 @@
       <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
+      <c r="D8" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -700,7 +697,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -717,8 +714,8 @@
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>32</v>
+      <c r="D10" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -736,7 +733,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -754,7 +751,7 @@
         <v>9</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -772,7 +769,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -790,7 +787,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -808,7 +805,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -826,7 +823,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -844,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -861,8 +858,8 @@
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>32</v>
+      <c r="D18" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -879,7 +876,7 @@
         <v>9</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -895,8 +892,8 @@
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>32</v>
+      <c r="D20" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -913,7 +910,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -929,8 +926,8 @@
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>32</v>
+      <c r="D22" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -947,28 +944,14 @@
         <v>9</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D25" s="6"/>
